--- a/data_lake/granizo/dt=2026-08-02/excel/PronosticoMunicipal_Granizo_72h.xlsx
+++ b/data_lake/granizo/dt=2026-08-02/excel/PronosticoMunicipal_Granizo_72h.xlsx
@@ -488,17 +488,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-07-31 07:00</t>
+          <t>2026-08-04 07:00</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-07-31 19:00</t>
+          <t>2026-08-04 19:00</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -506,17 +506,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>15223</t>
+          <t>27250</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Cubará</t>
+          <t>El Litoral Del San Juán</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>Chocó</t>
         </is>
       </c>
       <c r="J2" t="n">
